--- a/table/supp/workbooks/SuppTable_S3_Species_inventory_and_stability.xlsx
+++ b/table/supp/workbooks/SuppTable_S3_Species_inventory_and_stability.xlsx
@@ -1,37 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By class" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By superclass" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composition stability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Species summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By class" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By category" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Composition stability" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LowInput Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LowInput Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LowInput</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperClass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerolipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerophospholipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prenol Lipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatty Acyls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingolipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterol Lipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_accessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full_panel_pctTIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resample_lo95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resample_hi95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resample_halfwidth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loo_race_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loo_race_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loo_race_maxshift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIN</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,80 +181,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -173,10 +236,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -202,15 +261,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -236,6 +292,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -411,122 +468,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Control Total</t>
-        </is>
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LowInput Total</t>
-        </is>
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Control Only</t>
-        </is>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LowInput Only</t>
-        </is>
+      <c r="A6" t="s">
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All Unique</t>
-        </is>
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LowInput</t>
-        </is>
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TG</t>
-        </is>
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2" t="n">
         <v>67</v>
@@ -536,36 +562,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
+      <c r="A3" t="s">
+        <v>12</v>
       </c>
       <c r="B3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n">
         <v>36</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
+      <c r="A5" t="s">
+        <v>14</v>
       </c>
       <c r="B5" t="n">
         <v>16</v>
@@ -575,10 +595,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
+      <c r="A6" t="s">
+        <v>15</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -588,10 +606,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SQDG</t>
-        </is>
+      <c r="A7" t="s">
+        <v>16</v>
       </c>
       <c r="B7" t="n">
         <v>11</v>
@@ -601,10 +617,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DGDG</t>
-        </is>
+      <c r="A8" t="s">
+        <v>17</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
@@ -614,10 +628,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
+      <c r="A9" t="s">
+        <v>18</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
@@ -627,10 +639,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MGDG</t>
-        </is>
+      <c r="A10" t="s">
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>5</v>
@@ -640,10 +650,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LPC</t>
-        </is>
+      <c r="A11" t="s">
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -653,10 +661,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
+      <c r="A12" t="s">
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -666,10 +672,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+      <c r="A13" t="s">
+        <v>22</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -679,10 +683,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
+      <c r="A14" t="s">
+        <v>23</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
@@ -692,10 +694,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LPE</t>
-        </is>
+      <c r="A15" t="s">
+        <v>24</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -705,203 +705,142 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SuperClass</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LowInput</t>
-        </is>
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Glycerolipid</t>
-        </is>
+      <c r="A2" t="s">
+        <v>26</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C2" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Glycerophospholipid</t>
-        </is>
+      <c r="A3" t="s">
+        <v>27</v>
       </c>
       <c r="B3" t="n">
         <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ether lipid</t>
-        </is>
+      <c r="A4" t="s">
+        <v>28</v>
       </c>
       <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="n">
         <v>7</v>
       </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fatty acid</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sphingolipid</t>
-        </is>
+      <c r="A6" t="s">
+        <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Betaine lipid</t>
-        </is>
+      <c r="A7" t="s">
+        <v>31</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Terpenoid</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n_accessions</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>full_panel_pctTIC</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>resample_lo95</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resample_hi95</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>resample_halfwidth</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>loo_race_min</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>loo_race_max</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>loo_race_maxshift</t>
-        </is>
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>394</v>
@@ -929,15 +868,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>394</v>
@@ -961,19 +896,15 @@
         <v>0.0176611028004173</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000871846738312351</v>
+        <v>0.00087184673831235</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>394</v>
@@ -1001,15 +932,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LPC</t>
-        </is>
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>394</v>
@@ -1037,15 +964,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LPE</t>
-        </is>
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>394</v>
@@ -1060,7 +983,7 @@
         <v>0.00656384679475281</v>
       </c>
       <c r="G6" t="n">
-        <v>9.518854334925311e-05</v>
+        <v>0.0000951885433492531</v>
       </c>
       <c r="H6" t="n">
         <v>0.00643757871691847</v>
@@ -1069,19 +992,15 @@
         <v>0.0065706195442358</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000104036750236478</v>
+        <v>0.00010403675023647</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>394</v>
@@ -1109,15 +1028,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>394</v>
@@ -1132,7 +1047,7 @@
         <v>0.0144771843602299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000351526458095187</v>
+        <v>0.00035152645809518</v>
       </c>
       <c r="H8" t="n">
         <v>0.0140482021400509</v>
@@ -1141,19 +1056,15 @@
         <v>0.0143562033570116</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000198651413297949</v>
+        <v>0.00019865141329794</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>394</v>
@@ -1181,15 +1092,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DGDG</t>
-        </is>
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>394</v>
@@ -1217,15 +1124,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>394</v>
@@ -1253,15 +1156,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MGDG</t>
-        </is>
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>394</v>
@@ -1289,15 +1188,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SQDG</t>
-        </is>
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>394</v>
@@ -1325,15 +1220,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CTL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TG</t>
-        </is>
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
       </c>
       <c r="C14" t="n">
         <v>394</v>
@@ -1361,15 +1252,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>363</v>
@@ -1397,15 +1284,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>363</v>
@@ -1420,7 +1303,7 @@
         <v>0.0263527080302063</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000794299478887404</v>
+        <v>0.0007942994788874</v>
       </c>
       <c r="H16" t="n">
         <v>0.0253370026220241</v>
@@ -1429,19 +1312,15 @@
         <v>0.0257772704526994</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000263059340510945</v>
+        <v>0.00026305934051094</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>363</v>
@@ -1469,15 +1348,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LPC</t>
-        </is>
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>363</v>
@@ -1501,19 +1376,15 @@
         <v>0.15474073335733</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000534265850934301</v>
+        <v>0.0005342658509343</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LPE</t>
-        </is>
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>363</v>
@@ -1528,7 +1399,7 @@
         <v>0.0140997485762979</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000191500150626087</v>
+        <v>0.00019150015062608</v>
       </c>
       <c r="H19" t="n">
         <v>0.0138904292527279</v>
@@ -1537,19 +1408,15 @@
         <v>0.0139408414752768</v>
       </c>
       <c r="J19" t="n">
-        <v>3.13987323475248e-05</v>
+        <v>0.0000313987323475248</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
       </c>
       <c r="C20" t="n">
         <v>363</v>
@@ -1577,15 +1444,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>363</v>
@@ -1600,7 +1463,7 @@
         <v>0.0457710280575661</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000841264172855703</v>
+        <v>0.0008412641728557</v>
       </c>
       <c r="H21" t="n">
         <v>0.0444450614621297</v>
@@ -1609,19 +1472,15 @@
         <v>0.0452671437597786</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000506773967582384</v>
+        <v>0.00050677396758238</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
       </c>
       <c r="C22" t="n">
         <v>363</v>
@@ -1649,15 +1508,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DGDG</t>
-        </is>
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
       </c>
       <c r="C23" t="n">
         <v>363</v>
@@ -1685,15 +1540,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
       </c>
       <c r="C24" t="n">
         <v>363</v>
@@ -1721,15 +1572,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MGDG</t>
-        </is>
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
       </c>
       <c r="C25" t="n">
         <v>363</v>
@@ -1757,15 +1604,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SQDG</t>
-        </is>
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
       </c>
       <c r="C26" t="n">
         <v>363</v>
@@ -1780,7 +1623,7 @@
         <v>1.28498401332359</v>
       </c>
       <c r="G26" t="n">
-        <v>0.008327752695825639</v>
+        <v>0.00832775269582564</v>
       </c>
       <c r="H26" t="n">
         <v>1.27447032164453</v>
@@ -1793,15 +1636,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TG</t>
-        </is>
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
       </c>
       <c r="C27" t="n">
         <v>363</v>
@@ -1816,7 +1655,7 @@
         <v>4.95831878394636</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07000258005302171</v>
+        <v>0.0700025800530217</v>
       </c>
       <c r="H27" t="n">
         <v>4.85817159011696</v>
@@ -1829,6 +1668,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>